--- a/Report samples/Spraying Maintenance 2025.xlsx
+++ b/Report samples/Spraying Maintenance 2025.xlsx
@@ -72,13 +72,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="81">
   <si>
-    <t>POLIMA FOREST BINTULU SDN. BHD.  (Company No. 749886-W)</t>
+    <t>GREENACRE PLANTATIONS SDN. BHD.  (Company No. 000000-X)</t>
   </si>
   <si>
     <t>ESTATE MONTHLY REPORT</t>
   </si>
   <si>
-    <t>LADANG BATANG KAYAN</t>
+    <t>DEMO ESTATE</t>
   </si>
   <si>
     <t>GLYPHOSATE SPRAYING SELECT</t>
